--- a/outputs/InnovateUK_Funding_Opportunities_WeeklyBreakdown.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_WeeklyBreakdown.xlsx
@@ -481,13 +481,13 @@
         <v>46071</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -7728,7 +7728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8090,26 +8090,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>iX Challenge - Enabling regional carbon dioxide utilisation in Southwest Wales through geospatial intelligence</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-enabling-regional-carbon-dioxide-utilisation-southwest-wales/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-24 10:36</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46073.43888888889</v>
+        <v>46077.44166666667</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -8118,25 +8118,190 @@
       <c r="H7" t="b">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>46077</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>23/04/2026                              23:59</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>46113.45833333334</v>
+        <v>46135.99930555555</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="O7" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Semiconductors and components for smart electronic platforms</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:32</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>46073.43888888889</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Wednesday 1 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Robotics Adoption Hubs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:43</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>46077.44652777778</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Wednesday 15 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>£7.5 million</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Robotics Adoption Central Convening Body</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:43</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>46077.44652777778</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Wednesday 15 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="O10" s="1" t="n">
         <v>46071</v>
       </c>
     </row>

--- a/outputs/InnovateUK_Funding_Opportunities_WeeklyBreakdown.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_WeeklyBreakdown.xlsx
@@ -482,13 +482,13 @@
         <v>46078</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -8010,7 +8010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8323,6 +8323,295 @@
         <v>46078</v>
       </c>
       <c r="O5" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ARIA: Universal Fabricators - concept papers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-universal-fabricators-concept-papers/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-26 10:34</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>46079.44027777778</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>09/03/2026                              14:00</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>46090.58333333334</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>£50</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/adopt-facilitator-support-grant-round-7/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-26 10:34</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>46079.44027777778</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>08/04/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>46120.45833333334</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UK Defence Innovation Competition: Innovation Support to Operations Phase 3 (Cycle 7)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/uk-defence-innovation-competition-innovation-support-to-operations-phase-3-cycle-7/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-26 10:34</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>46079.44027777778</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>12/05/2026                              12:00</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>46154.5</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>£1.0 million</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Countering Illegal Use of UAS Around Prisons and Sensitive Sites</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/countering-illegal-use-of-uas-around-prisons-and-sensitive-sites/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-26 10:34</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>46079.44027777778</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>31/03/2026                              12:00</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>46112.5</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>£5,000</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-26 10:40</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>46079.44444444445</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Wednesday 8 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>46120.45833333334</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>£2,500</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="O10" s="1" t="n">
         <v>46078</v>
       </c>
     </row>

--- a/outputs/InnovateUK_Funding_Opportunities_WeeklyBreakdown.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_WeeklyBreakdown.xlsx
@@ -482,13 +482,13 @@
         <v>46078</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -8010,7 +8010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8801,26 +8801,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 7</t>
+          <t>ARIA: Enduring Atmospheric Platforms - full proposals</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-enduring-atmospheric-platforms-full-proposals/</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-26 10:40</t>
+          <t>2026-03-03 10:27</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>46079.44444444445</v>
+        <v>46084.43541666667</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -8829,25 +8829,137 @@
       <c r="H14" t="b">
         <v>0</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>01/03/2026</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>46082</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>02/04/2026                              12:00</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>46120.45833333334</v>
+        <v>46114.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£500</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="O14" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-02-26 10:40</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>46079.44444444445</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Wednesday 8 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>46120.45833333334</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>£2,500</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-03-03 10:34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>46084.44027777778</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Wednesday 1 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="O16" s="1" t="n">
         <v>46078</v>
       </c>
     </row>

--- a/outputs/InnovateUK_Funding_Opportunities_WeeklyBreakdown.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_WeeklyBreakdown.xlsx
@@ -487,10 +487,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -9171,7 +9171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9254,26 +9254,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/clean-maritime-demonstration-competition-7/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-03-12 10:27</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46092.44027777778</v>
+        <v>46093.43541666667</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -9282,11 +9282,17 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>46092</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>15/07/2026                              11:00</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -9294,7 +9300,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£6.0 million</t>
+          <t>£121.0 million</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
@@ -9312,12 +9318,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
+          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -9347,7 +9353,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£6.0 million</t>
         </is>
       </c>
       <c r="N3" s="2" t="n">
@@ -9365,12 +9371,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -9400,13 +9406,66 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£15.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="O4" s="1" t="n">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-11 10:34</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46092.44027777778</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Wednesday 15 July 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>46218.45833333334</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>£15.0 million</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>46092</v>
       </c>
     </row>
